--- a/data/trans_dic/MCS12_SP_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,95; 41,62</t>
+          <t>34,6; 41,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,07; 53,54</t>
+          <t>46,04; 53,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,55; 52,43</t>
+          <t>44,6; 52,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,54; 43,01</t>
+          <t>34,57; 42,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,03; 51,5</t>
+          <t>44,01; 51,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,67; 70,12</t>
+          <t>63,01; 70,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,0; 60,46</t>
+          <t>53,0; 60,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,0; 49,87</t>
+          <t>44,12; 49,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,08; 45,41</t>
+          <t>40,39; 45,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,13; 60,66</t>
+          <t>55,23; 60,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,9; 55,39</t>
+          <t>49,86; 55,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,22; 45,48</t>
+          <t>39,91; 45,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,85; 46,45</t>
+          <t>39,87; 46,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,49; 51,25</t>
+          <t>44,81; 51,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,49; 49,67</t>
+          <t>43,79; 50,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 42,62</t>
+          <t>17,51; 42,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,14; 59,81</t>
+          <t>52,85; 59,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,9; 61,16</t>
+          <t>54,88; 61,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,81; 57,29</t>
+          <t>50,9; 57,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,84; 51,57</t>
+          <t>45,97; 51,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,4; 52,01</t>
+          <t>47,45; 51,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,86; 55,5</t>
+          <t>50,79; 55,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,1; 52,5</t>
+          <t>48,22; 52,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,9; 45,77</t>
+          <t>25,61; 45,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,75; 47,73</t>
+          <t>40,14; 47,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 49,39</t>
+          <t>41,7; 49,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,46</t>
+          <t>39,09; 46,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,54; 44,88</t>
+          <t>36,35; 45,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,91; 58,48</t>
+          <t>51,18; 58,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,57; 62,73</t>
+          <t>55,34; 62,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,49; 52,64</t>
+          <t>45,43; 52,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,67; 78,17</t>
+          <t>46,18; 78,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,57; 52,13</t>
+          <t>46,34; 52,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,7; 54,98</t>
+          <t>49,88; 55,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,2; 48,4</t>
+          <t>43,31; 48,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,23; 68,25</t>
+          <t>43,37; 69,22</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,86; 50,04</t>
+          <t>43,56; 50,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,2; 55,9</t>
+          <t>49,05; 55,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,97; 57,28</t>
+          <t>50,95; 57,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 48,24</t>
+          <t>40,84; 47,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,99; 59,0</t>
+          <t>52,97; 58,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,28; 67,56</t>
+          <t>61,46; 67,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,94; 61,93</t>
+          <t>55,99; 62,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,83; 66,04</t>
+          <t>53,62; 65,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,31; 53,65</t>
+          <t>49,09; 53,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,25; 61,11</t>
+          <t>56,57; 60,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,41; 58,92</t>
+          <t>54,32; 58,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,84; 56,53</t>
+          <t>48,66; 57,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,41; 44,98</t>
+          <t>41,49; 45,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,28; 50,73</t>
+          <t>47,31; 50,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,4; 49,84</t>
+          <t>46,51; 50,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,37; 42,04</t>
+          <t>30,56; 42,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,47; 55,94</t>
+          <t>52,4; 56,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,19; 63,49</t>
+          <t>60,17; 63,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,1; 56,57</t>
+          <t>53,18; 56,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,04; 61,56</t>
+          <t>50,15; 62,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 50,01</t>
+          <t>47,47; 49,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,27; 56,69</t>
+          <t>54,39; 56,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50,42; 52,82</t>
+          <t>50,21; 52,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,95; 50,83</t>
+          <t>41,94; 51,27</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>235633; 288844</t>
+          <t>240157; 289060</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>324053; 376629</t>
+          <t>323866; 377157</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300620; 353802</t>
+          <t>300964; 355276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217639; 271037</t>
+          <t>217855; 269408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>303112; 354501</t>
+          <t>302964; 353349</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>436815; 488794</t>
+          <t>439185; 490055</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>356623; 406775</t>
+          <t>356622; 406707</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>294772; 334036</t>
+          <t>295509; 334360</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>554048; 627686</t>
+          <t>558358; 630841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>772083; 849610</t>
+          <t>773557; 847826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>672505; 746482</t>
+          <t>671943; 745635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>522879; 591245</t>
+          <t>518851; 590716</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>383323; 446749</t>
+          <t>383462; 447731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452860; 521673</t>
+          <t>456106; 521008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>444673; 507845</t>
+          <t>447715; 511548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211768; 506478</t>
+          <t>208024; 506050</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>514610; 579184</t>
+          <t>511750; 576581</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>566643; 631274</t>
+          <t>566425; 633564</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>529954; 597485</t>
+          <t>530833; 597590</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>436736; 491344</t>
+          <t>438064; 489229</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>914958; 1003846</t>
+          <t>915956; 1002551</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1042662; 1137784</t>
+          <t>1041254; 1129129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>993415; 1084291</t>
+          <t>995956; 1088156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>575942; 980036</t>
+          <t>548313; 981945</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>269698; 323841</t>
+          <t>272322; 324317</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316416; 374182</t>
+          <t>315926; 372782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298762; 352911</t>
+          <t>296934; 349530</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>256659; 315230</t>
+          <t>255292; 316351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>348117; 399941</t>
+          <t>349964; 399150</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>431859; 487484</t>
+          <t>430102; 488648</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>357064; 413195</t>
+          <t>356655; 412156</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>434777; 728289</t>
+          <t>430182; 734312</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>634418; 710226</t>
+          <t>631264; 708726</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>762822; 843906</t>
+          <t>765617; 847737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>667316; 747609</t>
+          <t>668974; 746458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>706367; 1115244</t>
+          <t>708655; 1131041</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>413238; 471504</t>
+          <t>410470; 473198</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>466271; 529818</t>
+          <t>464833; 529818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>477873; 537082</t>
+          <t>477706; 537613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>376904; 445197</t>
+          <t>376903; 441545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>550355; 612806</t>
+          <t>550109; 612492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>644588; 710681</t>
+          <t>646508; 708020</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>583919; 646431</t>
+          <t>584382; 647360</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>586370; 719329</t>
+          <t>584115; 717914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976670; 1062648</t>
+          <t>972306; 1064060</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1124888; 1221982</t>
+          <t>1131252; 1216824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1078004; 1167391</t>
+          <t>1076255; 1167371</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>982793; 1137565</t>
+          <t>979189; 1152127</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1356877; 1473889</t>
+          <t>1359326; 1474346</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1620190; 1738378</t>
+          <t>1621155; 1735304</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1575082; 1691855</t>
+          <t>1578751; 1701411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>976902; 1447636</t>
+          <t>1052445; 1456307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1773088; 1890301</t>
+          <t>1770768; 1893868</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2141823; 2259257</t>
+          <t>2141157; 2255406</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1882208; 2005086</t>
+          <t>1884984; 2012236</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1823309; 2243155</t>
+          <t>1827309; 2268094</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3167492; 3328852</t>
+          <t>3159395; 3321312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3790831; 3959656</t>
+          <t>3799360; 3968661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3498469; 3664912</t>
+          <t>3483912; 3659063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2972898; 3602461</t>
+          <t>2972143; 3633796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,6; 41,65</t>
+          <t>34,11; 41,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,04; 53,61</t>
+          <t>45,47; 53,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,6; 52,65</t>
+          <t>44,43; 52,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,57; 42,75</t>
+          <t>34,81; 42,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,01; 51,33</t>
+          <t>44,14; 51,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,01; 70,3</t>
+          <t>62,58; 69,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,0; 60,45</t>
+          <t>53,0; 60,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,12; 49,91</t>
+          <t>43,56; 50,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,39; 45,63</t>
+          <t>40,19; 45,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,23; 60,54</t>
+          <t>55,23; 60,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,86; 55,33</t>
+          <t>49,65; 55,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,91; 45,44</t>
+          <t>40,41; 45,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,87; 46,55</t>
+          <t>39,69; 46,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,81; 51,18</t>
+          <t>44,8; 51,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,79; 50,03</t>
+          <t>43,33; 49,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 42,59</t>
+          <t>38,25; 45,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,85; 59,54</t>
+          <t>53,16; 59,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,88; 61,38</t>
+          <t>54,96; 61,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,9; 57,3</t>
+          <t>50,56; 57,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 51,34</t>
+          <t>46,16; 51,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,45; 51,94</t>
+          <t>47,55; 52,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,79; 55,08</t>
+          <t>50,63; 55,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,22; 52,69</t>
+          <t>47,94; 52,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,61; 45,86</t>
+          <t>43,52; 47,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,14; 47,8</t>
+          <t>39,69; 47,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,7; 49,2</t>
+          <t>41,44; 49,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,09; 46,02</t>
+          <t>39,18; 46,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,35; 45,04</t>
+          <t>36,05; 44,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,18; 58,37</t>
+          <t>50,85; 58,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,34; 62,87</t>
+          <t>55,64; 62,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,43; 52,5</t>
+          <t>45,22; 52,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,18; 78,82</t>
+          <t>47,1; 53,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,34; 52,02</t>
+          <t>46,72; 52,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,88; 55,23</t>
+          <t>49,75; 55,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,31; 48,33</t>
+          <t>43,3; 48,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,37; 69,22</t>
+          <t>42,93; 47,94</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,56; 50,22</t>
+          <t>43,41; 49,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,05; 55,9</t>
+          <t>49,57; 55,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,95; 57,34</t>
+          <t>50,7; 57,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 47,84</t>
+          <t>42,31; 48,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,97; 58,97</t>
+          <t>52,59; 58,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,46; 67,31</t>
+          <t>61,52; 67,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,99; 62,02</t>
+          <t>55,83; 61,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,62; 65,91</t>
+          <t>52,64; 57,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,09; 53,72</t>
+          <t>49,16; 53,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,57; 60,85</t>
+          <t>56,41; 61,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,32; 58,92</t>
+          <t>54,32; 58,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,66; 57,26</t>
+          <t>48,31; 52,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,49; 45,0</t>
+          <t>41,5; 44,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,31; 50,64</t>
+          <t>47,21; 50,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,51; 50,12</t>
+          <t>46,25; 49,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,56; 42,29</t>
+          <t>40,03; 43,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,4; 56,04</t>
+          <t>52,49; 55,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,38</t>
+          <t>60,19; 63,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,18; 56,77</t>
+          <t>52,98; 56,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,15; 62,25</t>
+          <t>49,42; 52,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,47; 49,9</t>
+          <t>47,5; 49,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,39; 56,82</t>
+          <t>54,36; 56,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50,21; 52,73</t>
+          <t>50,28; 52,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,94; 51,27</t>
+          <t>45,3; 47,61</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243583</t>
+          <t>263931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>314459</t>
+          <t>341102</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>558042</t>
+          <t>605033</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>240157; 289060</t>
+          <t>236741; 288864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>323866; 377157</t>
+          <t>319857; 376046</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300964; 355276</t>
+          <t>299788; 353106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217855; 269408</t>
+          <t>238369; 291934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>302964; 353349</t>
+          <t>303837; 355689</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>439185; 490055</t>
+          <t>436244; 486969</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>356622; 406707</t>
+          <t>356622; 408046</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>295509; 334360</t>
+          <t>316701; 363783</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>558358; 630841</t>
+          <t>555541; 626877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>773557; 847826</t>
+          <t>773551; 846552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>671943; 745635</t>
+          <t>669080; 742067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>518851; 590716</t>
+          <t>570454; 638509</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391503</t>
+          <t>436982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>464161</t>
+          <t>523193</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>855664</t>
+          <t>960176</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>383462; 447731</t>
+          <t>381707; 445235</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>456106; 521008</t>
+          <t>456012; 522804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>447715; 511548</t>
+          <t>443007; 509702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>208024; 506050</t>
+          <t>399257; 473246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>511750; 576581</t>
+          <t>514838; 580535</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>566425; 633564</t>
+          <t>567302; 631840</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>530833; 597590</t>
+          <t>527302; 595253</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>438064; 489229</t>
+          <t>491622; 551924</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>915956; 1002551</t>
+          <t>917871; 1008975</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1041254; 1129129</t>
+          <t>1037977; 1130277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>995956; 1088156</t>
+          <t>990067; 1081321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>548313; 981945</t>
+          <t>917847; 1010034</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284976</t>
+          <t>321866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>554651</t>
+          <t>408582</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>839626</t>
+          <t>730448</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272322; 324317</t>
+          <t>269281; 322011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315926; 372782</t>
+          <t>313983; 372715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>296934; 349530</t>
+          <t>297629; 352063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255292; 316351</t>
+          <t>288541; 352546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>349964; 399150</t>
+          <t>347748; 401317</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>430102; 488648</t>
+          <t>432416; 489269</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>356655; 412156</t>
+          <t>354993; 410194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>430182; 734312</t>
+          <t>381681; 435265</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>631264; 708726</t>
+          <t>636492; 710575</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>765617; 847737</t>
+          <t>763485; 847172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>668974; 746458</t>
+          <t>668734; 748249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>708655; 1131041</t>
+          <t>691516; 772153</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>410482</t>
+          <t>448203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>627160</t>
+          <t>613311</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1037641</t>
+          <t>1061514</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>410470; 473198</t>
+          <t>409030; 470106</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>464833; 529818</t>
+          <t>469751; 527939</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>477706; 537613</t>
+          <t>475372; 541820</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>376903; 441545</t>
+          <t>417225; 481930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>550109; 612492</t>
+          <t>546154; 610344</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>646508; 708020</t>
+          <t>647129; 709027</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>584382; 647360</t>
+          <t>582735; 645174</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>584115; 717914</t>
+          <t>585965; 643002</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>972306; 1064060</t>
+          <t>973847; 1066708</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1131252; 1216824</t>
+          <t>1127994; 1220551</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1076255; 1167371</t>
+          <t>1076190; 1165712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>979189; 1152127</t>
+          <t>1014067; 1103709</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1359326; 1474346</t>
+          <t>1359732; 1472819</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1621155; 1735304</t>
+          <t>1617919; 1741217</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1578751; 1701411</t>
+          <t>1569963; 1684833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1052445; 1456307</t>
+          <t>1407074; 1533452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1770768; 1893868</t>
+          <t>1773654; 1890895</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2141157; 2255406</t>
+          <t>2141732; 2263726</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1884984; 2012236</t>
+          <t>1877885; 2002874</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1827309; 2268094</t>
+          <t>1836258; 1940212</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3159395; 3321312</t>
+          <t>3161364; 3326987</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3799360; 3968661</t>
+          <t>3797016; 3961862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3483912; 3659063</t>
+          <t>3488953; 3660935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2972143; 3633796</t>
+          <t>3275867; 3442213</t>
         </is>
       </c>
     </row>
